--- a/docs/control-plane/03_REPOSITORY_REGISTRY.xlsx
+++ b/docs/control-plane/03_REPOSITORY_REGISTRY.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="94">
   <si>
     <t>03_REPOSITORY_REGISTRY</t>
   </si>
@@ -46,6 +46,12 @@
     <t>CRITICAL: NEVER STORE PASSWORDS, API KEYS, SERVICE-ROLE KEYS, PRIVATE CERTIFICATES, SMTP PASSWORDS, OR R2 SECRETS IN THIS WORKBOOK. USE SECURE ENVIRONMENT REFERENCES ONLY.</t>
   </si>
   <si>
+    <t>Canonical Production Subdomain</t>
+  </si>
+  <si>
+    <t>https://erp.arivahly.in (Parent domain: arivahly.in)</t>
+  </si>
+  <si>
     <t>AI Operating Constraint 1</t>
   </si>
   <si>
@@ -70,10 +76,16 @@
     <t>UNKNOWN means unknown. Do not guess. If a field is uncertain, record NEEDS_VERIFICATION.</t>
   </si>
   <si>
+    <t>MCP Security Boundary</t>
+  </si>
+  <si>
+    <t>MCP is DISABLED and BLOCKED from public routing. MCP tools must remain internal/local only.</t>
+  </si>
+  <si>
     <t>Last Audit Date</t>
   </si>
   <si>
-    <t>2026-09-05T13:10:00+05:30 (Release v1.1.2-online-production-hardened)</t>
+    <t>2026-09-05T13:20:00+05:30 (Release v1.1.2-online-production-hardened)</t>
   </si>
   <si>
     <t>Repository_ID</t>
@@ -160,7 +172,7 @@
     <t>v1.1.2-online-production-hardened</t>
   </si>
   <si>
-    <t>bf0c7c75043b13fcb10b112ed981ef54a39f44f0</t>
+    <t>HEAD</t>
   </si>
   <si>
     <t>2026-09-05</t>
@@ -277,7 +289,7 @@
     <t>RELEASED</t>
   </si>
   <si>
-    <t>Final online managed SaaS hardening &amp; Cloudflare security baseline</t>
+    <t>Final online managed SaaS hardening &amp; Cloudflare security baseline for erp.arivahly.in</t>
   </si>
   <si>
     <t>Mirrored on origin remote</t>
@@ -731,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -816,6 +828,22 @@
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -840,7 +868,7 @@
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="29" customWidth="1"/>
     <col min="11" max="12" width="37" customWidth="1"/>
-    <col min="13" max="13" width="44" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -849,214 +877,214 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="Q3" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1081,71 +1109,71 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1161,7 +1189,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
@@ -1170,106 +1198,106 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>86</v>
+      <c r="F2" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>86</v>
+        <v>53</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>86</v>
+        <v>53</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/control-plane/03_REPOSITORY_REGISTRY.xlsx
+++ b/docs/control-plane/03_REPOSITORY_REGISTRY.xlsx
@@ -172,7 +172,7 @@
     <t>v1.1.2-online-production-hardened</t>
   </si>
   <si>
-    <t>HEAD</t>
+    <t>4f1c5da05d4b88705182c31a44c4d5b768dead50</t>
   </si>
   <si>
     <t>2026-09-05</t>
@@ -868,7 +868,7 @@
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="29" customWidth="1"/>
     <col min="11" max="12" width="37" customWidth="1"/>
-    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="13" max="13" width="44" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -1189,7 +1189,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="7" width="14" customWidth="1"/>
